--- a/notes/LIBELLULA journal.xlsx
+++ b/notes/LIBELLULA journal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive\Desktop\Libellula\notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0037e56ddff3a368/Desktop/Libellula/notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABF8704-F42D-4ADD-B462-98794C3F457C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1ABF8704-F42D-4ADD-B462-98794C3F457C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCAE8843-0306-4583-AB2B-71E159B6B122}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CC99F97F-3E72-4FEA-AA64-B39819E65309}"/>
   </bookViews>
@@ -325,7 +325,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -668,7 +668,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A98371-216A-4D1C-8D7B-786B21A1BFEF}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="120" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="150" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.7109375" style="10" customWidth="1"/>
     <col min="3" max="3" width="30.7109375" style="2" customWidth="1"/>
@@ -739,7 +739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -765,7 +765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -791,7 +791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>28</v>
       </c>
@@ -817,7 +817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>29</v>
       </c>
@@ -830,7 +830,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>34</v>
       </c>

--- a/notes/LIBELLULA journal.xlsx
+++ b/notes/LIBELLULA journal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0037e56ddff3a368/Desktop/Libellula/notes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive\Desktop\Libellula\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1ABF8704-F42D-4ADD-B462-98794C3F457C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCAE8843-0306-4583-AB2B-71E159B6B122}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACF7916-EFB3-44C1-82C7-E4E40F0748CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CC99F97F-3E72-4FEA-AA64-B39819E65309}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>PLANEJAMENTO LIBELLULA (secreto)</t>
   </si>
@@ -170,6 +170,18 @@
   </si>
   <si>
     <t>Indeterminado-indeterminado</t>
+  </si>
+  <si>
+    <t>Quarta-feira, 25/02/26</t>
+  </si>
+  <si>
+    <t>23h00-01h30</t>
+  </si>
+  <si>
+    <t>Sem trabalho executado</t>
+  </si>
+  <si>
+    <t>1) Separação entre notebooks com o método 'setup()' e com o modelo EPF. Antes estavam no mesmo notebook. Agora viraram dois diferentes.                                                              2) Criei um 'setup.py' na pasta 'src/' para permitir a importação ilimitada do método para todos os notebooks. O 'setup.py' está em 'src/'.</t>
   </si>
 </sst>
 </file>
@@ -667,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A98371-216A-4D1C-8D7B-786B21A1BFEF}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="150" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.7109375" style="10" customWidth="1"/>
@@ -824,8 +836,21 @@
       <c r="B8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="E8" s="12"/>
+      <c r="C8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>20</v>
+      </c>
       <c r="H8" s="24" t="s">
         <v>33</v>
       </c>
@@ -840,11 +865,44 @@
       <c r="C9" s="23" t="s">
         <v>31</v>
       </c>
+      <c r="D9" s="17" t="s">
+        <v>18</v>
+      </c>
       <c r="E9" s="12" t="s">
         <v>32</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/notes/LIBELLULA journal.xlsx
+++ b/notes/LIBELLULA journal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive\Desktop\Libellula\notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0037e56ddff3a368/Desktop/Libellula/notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACF7916-EFB3-44C1-82C7-E4E40F0748CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6ACF7916-EFB3-44C1-82C7-E4E40F0748CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23401C8E-4103-4CAB-9541-FABC8B670F63}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CC99F97F-3E72-4FEA-AA64-B39819E65309}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t>PLANEJAMENTO LIBELLULA (secreto)</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Começo-fim</t>
   </si>
   <si>
-    <t xml:space="preserve">1) Repositório criado (segundo a lista de afazeres semanais)                 2) Repositório do Libellula conectado ao ChatGPT via Códex            </t>
-  </si>
-  <si>
     <t>1) Criei o arquivo de código para as ferramentas financeiras a serem aplicadas ao dataset OHLC original. Mas ainda falta muito.</t>
   </si>
   <si>
@@ -114,6 +111,43 @@
   </si>
   <si>
     <t>1) Iniciei a codificação de um método para pré-processamento de dados financeiros, mas ainda falta muito pra coisa toda avançar.</t>
+  </si>
+  <si>
+    <t>Sexta-feira, 13/02/26</t>
+  </si>
+  <si>
+    <t>Sexta-feira, 20/02/26</t>
+  </si>
+  <si>
+    <t>16h31-indeterminado</t>
+  </si>
+  <si>
+    <t>1) EXTRAORDINÁRIO PROGRESSO! Constuir um EPF com 93% de eficiência! NEM O CHATGPT ACREDITOU!</t>
+  </si>
+  <si>
+    <t>1) Terminei o EPF! Ele está tão bom que nem dá pra acreditar! Criei uma rotina para descobrir qual indicador econômico influiu mais na eficiencia do EPF, e foi o oscilador estocástico rápido de 10 períodos (%K10)</t>
+  </si>
+  <si>
+    <t>NEM ME LEMBRO DE NADA DO QUE ACONTECEU NESSE DIA!</t>
+  </si>
+  <si>
+    <t>Domingo, 22/02/26</t>
+  </si>
+  <si>
+    <t>Indeterminado-indeterminado</t>
+  </si>
+  <si>
+    <t>Quarta-feira, 25/02/26</t>
+  </si>
+  <si>
+    <t>23h00-01h30</t>
+  </si>
+  <si>
+    <t>Sem trabalho executado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Repositório criado (segundo a lista de afazeres semanais)
+2) Repositório do Libellula conectado ao ChatGPT via Códex            </t>
   </si>
   <si>
     <r>
@@ -128,7 +162,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Progredi muito pouco  </t>
+      <t xml:space="preserve">Progredi muito pouco
+</t>
     </r>
     <r>
       <rPr>
@@ -138,50 +173,27 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">                     2) EPFs precisam de pré-processamento complexo, com métodos orientados ao objeto, preferencialmente.   </t>
+      <t xml:space="preserve">2) EPFs precisam de pré-processamento complexo, com métodos orientados ao objeto, preferencialmente.   </t>
     </r>
   </si>
   <si>
-    <t>Demanda-se um aprofundamento teórico no conceito de EPF para drawndown futuro. Um método 'setup' está sendo criado para automatizar o pré-processamento dos dados.</t>
-  </si>
-  <si>
-    <t>Proposta de cronograma: diário, de madrugada, por 30 dias ininterruptos, uma hora e meia por madrugada, a começar na madrugada de amanhã (de 10/02/26 até 12/03/26)</t>
-  </si>
-  <si>
-    <t>Sexta-feira, 13/02/26</t>
-  </si>
-  <si>
-    <t>Sexta-feira, 20/02/26</t>
-  </si>
-  <si>
-    <t>16h31-indeterminado</t>
-  </si>
-  <si>
-    <t>1) EXTRAORDINÁRIO PROGRESSO! Constuir um EPF com 93% de eficiência! NEM O CHATGPT ACREDITOU!</t>
-  </si>
-  <si>
-    <t>1) Terminei o EPF! Ele está tão bom que nem dá pra acreditar! Criei uma rotina para descobrir qual indicador econômico influiu mais na eficiencia do EPF, e foi o oscilador estocástico rápido de 10 períodos (%K10)</t>
-  </si>
-  <si>
-    <t>NEM ME LEMBRO DE NADA DO QUE ACONTECEU NESSE DIA!</t>
-  </si>
-  <si>
-    <t>Domingo, 22/02/26</t>
-  </si>
-  <si>
-    <t>Indeterminado-indeterminado</t>
-  </si>
-  <si>
-    <t>Quarta-feira, 25/02/26</t>
-  </si>
-  <si>
-    <t>23h00-01h30</t>
-  </si>
-  <si>
-    <t>Sem trabalho executado</t>
-  </si>
-  <si>
-    <t>1) Separação entre notebooks com o método 'setup()' e com o modelo EPF. Antes estavam no mesmo notebook. Agora viraram dois diferentes.                                                              2) Criei um 'setup.py' na pasta 'src/' para permitir a importação ilimitada do método para todos os notebooks. O 'setup.py' está em 'src/'.</t>
+    <t>1) Separação entre notebooks com o método 'setup()' e com o modelo EPF. Antes estavam no mesmo notebook. Agora viraram dois diferentes.
+ 2) Criei um 'setup.py' na pasta 'src/' para permitir a importação ilimitada do método para todos os notebooks. O 'setup.py' está em 'src/'.</t>
+  </si>
+  <si>
+    <t>Proposta de cronograma: diário, de madrugada, pelo menos 1 hora por noite, toda noite</t>
+  </si>
+  <si>
+    <t>Todas as atualizações registradas IMPLICAM O 'COMMIT' NO REPOSITÓRIO REMOTO DO PROJETO!</t>
+  </si>
+  <si>
+    <t>by: Miguel Ferreira</t>
+  </si>
+  <si>
+    <t>https://github.com/miguelrferreiraf/libellula</t>
+  </si>
+  <si>
+    <t>1) Demanda-se um aprofundamento teórico no conceito de EPF para drawndown futuro. Um método 'setup' está sendo criado para automatizar o pré-processamento dos dados.</t>
   </si>
 </sst>
 </file>
@@ -213,7 +225,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +268,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6600"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3737"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -267,16 +291,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color theme="2" tint="-0.499984740745262"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color theme="2" tint="-0.499984740745262"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="2" tint="-0.499984740745262"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="2" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -284,62 +308,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -348,6 +379,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF3737"/>
+      <color rgb="FFFF6600"/>
       <color rgb="FFEF9F9F"/>
     </mruColors>
   </colors>
@@ -679,226 +712,252 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A98371-216A-4D1C-8D7B-786B21A1BFEF}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="150" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.7109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" style="21" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" style="5" customWidth="1"/>
+    <col min="1" max="2" width="12.7109375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" style="28" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" style="29" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" style="30" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" style="31" customWidth="1"/>
     <col min="7" max="7" width="30.7109375" style="19" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="H1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
+      <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-    </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="D11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="18" t="s">
+      <c r="G11" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="17" t="s">
+    </row>
+    <row r="12" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="18" t="s">
+      <c r="G12" s="19" t="s">
         <v>19</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
